--- a/Result/profitability/2028.xlsx
+++ b/Result/profitability/2028.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.76</v>
       </c>
       <c r="M2" t="n">
-        <v>0.17625</v>
+        <v>0.19375</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8225</v>
+        <v>5.02375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.89</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2775</v>
+        <v>0.2875</v>
       </c>
       <c r="N3" t="n">
-        <v>5.47625</v>
+        <v>5.6825</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.26</v>
+        <v>0.27875</v>
       </c>
       <c r="N4" t="n">
-        <v>5.784999999999999</v>
+        <v>5.93</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-3.92</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.23875</v>
+        <v>-0.23</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6624999999999996</v>
+        <v>-0.5700000000000003</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.25375</v>
+        <v>-0.21125</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.60625</v>
+        <v>0.06500000000000006</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1266,10 +1266,10 @@
         <v>0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.185</v>
+        <v>-0.18</v>
       </c>
       <c r="N7" t="n">
-        <v>0.39125</v>
+        <v>0.39875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1393,10 +1393,10 @@
         <v>0.17</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.18625</v>
+        <v>-0.1775</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7712499999999999</v>
+        <v>0.83375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1462499999999999</v>
+        <v>-0.14625</v>
       </c>
       <c r="N9" t="n">
         <v>2.19875</v>
@@ -1779,7 +1779,7 @@
         <v>-0.23</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8812499999999995</v>
+        <v>0.88125</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1903,10 +1903,10 @@
         <v>-0.2</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2549999999999999</v>
+        <v>-0.255</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3299999999999995</v>
+        <v>0.33</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2033,7 +2033,7 @@
         <v>0.25375</v>
       </c>
       <c r="N13" t="n">
-        <v>6.604999999999999</v>
+        <v>6.605</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2391</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2259</v>
+      </c>
+      <c r="E75" t="n">
+        <v>133</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="G75" t="n">
+        <v>73</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.06%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>12</v>
+      </c>
+      <c r="J75" t="n">
+        <v>86</v>
+      </c>
+      <c r="K75" t="n">
+        <v>72</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.10875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.16375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4666666666666668</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0990099009900991</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4666666666666668</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.7400000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
